--- a/input/timetable/Магистратура_Биология.xlsx
+++ b/input/timetable/Магистратура_Биология.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="59">
   <si>
     <t>пара</t>
   </si>
@@ -71,6 +71,9 @@
     <t>Зав. кафедрой</t>
   </si>
   <si>
+    <t>Преподаватель</t>
+  </si>
+  <si>
     <t>Направление</t>
   </si>
   <si>
@@ -122,9 +125,15 @@
     <t>Самоорганизация и саморазвитие (лек 16 ч)</t>
   </si>
   <si>
+    <t>Макарова Т.А.</t>
+  </si>
+  <si>
     <t>Самоорганизация и саморазвитие  (пр), ЭОиДОТ//Лидерство и командная работа при разработке и реализации проектов (пр), ЭОиДОТ</t>
   </si>
   <si>
+    <t>Малагин Д.В.</t>
+  </si>
+  <si>
     <t>День самостоятельной работы</t>
   </si>
   <si>
@@ -152,12 +161,30 @@
     <t>Флора и фауна Западной Сибири (пр), А623// Биотехнологии сохранения и воспроизводства растений (пр), А639</t>
   </si>
   <si>
+    <t>Стариков В.П./Макарова Т.А.</t>
+  </si>
+  <si>
     <t>Методика преподавания биологических дисциплин (лек)/(пр), А639</t>
   </si>
   <si>
     <t>Методика преподавания биологических дисциплин (пр), А639//</t>
   </si>
   <si>
+    <t>Сарапульцева Е.С./Макаров П.Н.</t>
+  </si>
+  <si>
+    <t>Макаров П.Н.</t>
+  </si>
+  <si>
+    <t>Усаева Н.Р.</t>
+  </si>
+  <si>
+    <t>Лукиянчина Е.В.</t>
+  </si>
+  <si>
+    <t>Усаева Н.Р./Лукиянчина Е.В.</t>
+  </si>
+  <si>
     <t>Современная экология и глобальные экологические проблемы (лек)/(пр), ЭОиДОТ</t>
   </si>
   <si>
@@ -168,6 +195,9 @@
   </si>
   <si>
     <t>//Спецпрактикум по биоразнообразию и охране природы (пр), А620</t>
+  </si>
+  <si>
+    <t>Матковский А.В.</t>
   </si>
 </sst>
 </file>
@@ -268,7 +298,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -287,12 +317,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="27">
+  <borders count="32">
     <border>
       <left/>
       <right/>
@@ -372,6 +408,64 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -617,6 +711,17 @@
     </border>
     <border>
       <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
@@ -632,7 +737,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -665,30 +770,34 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -704,6 +813,7 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -714,14 +824,15 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
@@ -737,13 +848,36 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -752,72 +886,32 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -825,16 +919,37 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1166,7 +1281,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -1175,10 +1290,11 @@
     <col min="4" max="4" width="16.85546875" style="2" customWidth="1"/>
     <col min="5" max="5" width="16.140625" style="2" customWidth="1"/>
     <col min="6" max="6" width="17.5703125" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -1186,15 +1302,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -1202,86 +1318,86 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="37" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="37"/>
-      <c r="E6" s="38">
+      <c r="C6" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="41"/>
+      <c r="E6" s="42">
         <v>1</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="39" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="39"/>
-      <c r="E7" s="40" t="s">
-        <v>38</v>
+      <c r="D7" s="43"/>
+      <c r="E7" s="44" t="s">
+        <v>41</v>
       </c>
       <c r="F7" s="13" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A8" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="37" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="41"/>
-      <c r="E8" s="41"/>
-    </row>
-    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>28</v>
+      </c>
+      <c r="C8" s="41" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="45"/>
+      <c r="E8" s="45"/>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" s="54" t="s">
-        <v>40</v>
-      </c>
-      <c r="D9" s="54"/>
-      <c r="E9" s="54"/>
-    </row>
-    <row r="10" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>30</v>
+      </c>
+      <c r="C9" s="50" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="50"/>
+      <c r="E9" s="50"/>
+    </row>
+    <row r="10" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B10" s="15" t="s">
         <v>0</v>
@@ -1292,250 +1408,297 @@
       <c r="D10" s="17"/>
       <c r="E10" s="18"/>
       <c r="F10" s="19"/>
-    </row>
-    <row r="11" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="21">
+      <c r="G10" s="20" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="22">
         <v>6</v>
       </c>
-      <c r="C11" s="67"/>
-      <c r="D11" s="68"/>
-      <c r="E11" s="68"/>
-      <c r="F11" s="69"/>
-    </row>
-    <row r="12" spans="1:6" ht="56.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="22"/>
-      <c r="B12" s="23">
+      <c r="C11" s="72"/>
+      <c r="D11" s="73"/>
+      <c r="E11" s="73"/>
+      <c r="F11" s="74"/>
+      <c r="G11" s="23"/>
+    </row>
+    <row r="12" spans="1:7" ht="56.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="24"/>
+      <c r="B12" s="25">
         <v>7</v>
       </c>
-      <c r="C12" s="70" t="s">
+      <c r="C12" s="75" t="s">
+        <v>35</v>
+      </c>
+      <c r="D12" s="76"/>
+      <c r="E12" s="76"/>
+      <c r="F12" s="77"/>
+      <c r="G12" s="47" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="26"/>
+      <c r="B13" s="27">
+        <v>8</v>
+      </c>
+      <c r="C13" s="78" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" s="79"/>
+      <c r="E13" s="79"/>
+      <c r="F13" s="80"/>
+      <c r="G13" s="48" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A14" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="22">
+        <v>6</v>
+      </c>
+      <c r="C14" s="81"/>
+      <c r="D14" s="82"/>
+      <c r="E14" s="82"/>
+      <c r="F14" s="83"/>
+      <c r="G14" s="29"/>
+    </row>
+    <row r="15" spans="1:7" ht="58.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="24"/>
+      <c r="B15" s="25">
+        <v>7</v>
+      </c>
+      <c r="C15" s="60" t="s">
+        <v>56</v>
+      </c>
+      <c r="D15" s="61"/>
+      <c r="E15" s="61"/>
+      <c r="F15" s="62"/>
+      <c r="G15" s="47" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="30"/>
+      <c r="B16" s="27">
+        <v>8</v>
+      </c>
+      <c r="C16" s="84" t="s">
+        <v>57</v>
+      </c>
+      <c r="D16" s="85"/>
+      <c r="E16" s="85"/>
+      <c r="F16" s="86"/>
+      <c r="G16" s="47" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A17" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="22">
+        <v>6</v>
+      </c>
+      <c r="C17" s="57"/>
+      <c r="D17" s="58"/>
+      <c r="E17" s="58"/>
+      <c r="F17" s="59"/>
+      <c r="G17" s="29"/>
+    </row>
+    <row r="18" spans="1:7" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="24"/>
+      <c r="B18" s="25">
+        <v>7</v>
+      </c>
+      <c r="C18" s="60" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" s="61"/>
+      <c r="E18" s="61"/>
+      <c r="F18" s="62"/>
+      <c r="G18" s="47" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="30"/>
+      <c r="B19" s="27">
+        <v>8</v>
+      </c>
+      <c r="C19" s="54" t="s">
+        <v>55</v>
+      </c>
+      <c r="D19" s="55"/>
+      <c r="E19" s="55"/>
+      <c r="F19" s="56"/>
+      <c r="G19" s="48" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A20" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" s="22">
+        <v>6</v>
+      </c>
+      <c r="C20" s="87"/>
+      <c r="D20" s="88"/>
+      <c r="E20" s="88"/>
+      <c r="F20" s="89"/>
+      <c r="G20" s="29"/>
+    </row>
+    <row r="21" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="24"/>
+      <c r="B21" s="25">
+        <v>7</v>
+      </c>
+      <c r="C21" s="60" t="s">
+        <v>44</v>
+      </c>
+      <c r="D21" s="61"/>
+      <c r="E21" s="61"/>
+      <c r="F21" s="62"/>
+      <c r="G21" s="47" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="30"/>
+      <c r="B22" s="27">
+        <v>8</v>
+      </c>
+      <c r="C22" s="54" t="s">
+        <v>45</v>
+      </c>
+      <c r="D22" s="55"/>
+      <c r="E22" s="55"/>
+      <c r="F22" s="56"/>
+      <c r="G22" s="48" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A23" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" s="22">
+        <v>6</v>
+      </c>
+      <c r="C23" s="57"/>
+      <c r="D23" s="58"/>
+      <c r="E23" s="58"/>
+      <c r="F23" s="59"/>
+      <c r="G23" s="29"/>
+    </row>
+    <row r="24" spans="1:7" ht="41.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="31"/>
+      <c r="B24" s="25">
+        <v>7</v>
+      </c>
+      <c r="C24" s="60" t="s">
+        <v>47</v>
+      </c>
+      <c r="D24" s="61"/>
+      <c r="E24" s="61"/>
+      <c r="F24" s="62"/>
+      <c r="G24" s="47" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="32"/>
+      <c r="B25" s="27">
+        <v>8</v>
+      </c>
+      <c r="C25" s="60" t="s">
+        <v>48</v>
+      </c>
+      <c r="D25" s="61"/>
+      <c r="E25" s="61"/>
+      <c r="F25" s="62"/>
+      <c r="G25" s="47" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="B26" s="34">
+        <v>1</v>
+      </c>
+      <c r="C26" s="63" t="s">
+        <v>37</v>
+      </c>
+      <c r="D26" s="64"/>
+      <c r="E26" s="64"/>
+      <c r="F26" s="65"/>
+      <c r="G26" s="29"/>
+    </row>
+    <row r="27" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A27" s="35"/>
+      <c r="B27" s="27">
+        <v>2</v>
+      </c>
+      <c r="C27" s="66"/>
+      <c r="D27" s="67"/>
+      <c r="E27" s="67"/>
+      <c r="F27" s="68"/>
+      <c r="G27" s="46"/>
+    </row>
+    <row r="28" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A28" s="36"/>
+      <c r="B28" s="37"/>
+      <c r="C28" s="69"/>
+      <c r="D28" s="70"/>
+      <c r="E28" s="70"/>
+      <c r="F28" s="71"/>
+      <c r="G28" s="38"/>
+    </row>
+    <row r="29" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="39"/>
+      <c r="B29" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="C29" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="D12" s="71"/>
-      <c r="E12" s="71"/>
-      <c r="F12" s="72"/>
-    </row>
-    <row r="13" spans="1:6" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="24"/>
-      <c r="B13" s="25">
-        <v>8</v>
-      </c>
-      <c r="C13" s="73" t="s">
-        <v>45</v>
-      </c>
-      <c r="D13" s="74"/>
-      <c r="E13" s="74"/>
-      <c r="F13" s="75"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A14" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" s="21">
-        <v>6</v>
-      </c>
-      <c r="C14" s="76"/>
-      <c r="D14" s="77"/>
-      <c r="E14" s="77"/>
-      <c r="F14" s="78"/>
-    </row>
-    <row r="15" spans="1:6" ht="58.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="22"/>
-      <c r="B15" s="23">
-        <v>7</v>
-      </c>
-      <c r="C15" s="45" t="s">
-        <v>47</v>
-      </c>
-      <c r="D15" s="46"/>
-      <c r="E15" s="46"/>
-      <c r="F15" s="47"/>
-    </row>
-    <row r="16" spans="1:6" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="27"/>
-      <c r="B16" s="25">
-        <v>8</v>
-      </c>
-      <c r="C16" s="79" t="s">
-        <v>48</v>
-      </c>
-      <c r="D16" s="80"/>
-      <c r="E16" s="80"/>
-      <c r="F16" s="81"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A17" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="B17" s="21">
-        <v>6</v>
-      </c>
-      <c r="C17" s="42"/>
-      <c r="D17" s="43"/>
-      <c r="E17" s="43"/>
-      <c r="F17" s="44"/>
-    </row>
-    <row r="18" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="22"/>
-      <c r="B18" s="23">
-        <v>7</v>
-      </c>
-      <c r="C18" s="45" t="s">
-        <v>46</v>
-      </c>
-      <c r="D18" s="46"/>
-      <c r="E18" s="46"/>
-      <c r="F18" s="47"/>
-    </row>
-    <row r="19" spans="1:6" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="27"/>
-      <c r="B19" s="25">
-        <v>8</v>
-      </c>
-      <c r="C19" s="48" t="s">
-        <v>46</v>
-      </c>
-      <c r="D19" s="49"/>
-      <c r="E19" s="49"/>
-      <c r="F19" s="50"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A20" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="B20" s="21">
-        <v>6</v>
-      </c>
-      <c r="C20" s="51"/>
-      <c r="D20" s="52"/>
-      <c r="E20" s="52"/>
-      <c r="F20" s="53"/>
-    </row>
-    <row r="21" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="22"/>
-      <c r="B21" s="23">
-        <v>7</v>
-      </c>
-      <c r="C21" s="45" t="s">
-        <v>41</v>
-      </c>
-      <c r="D21" s="46"/>
-      <c r="E21" s="46"/>
-      <c r="F21" s="47"/>
-    </row>
-    <row r="22" spans="1:6" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="27"/>
-      <c r="B22" s="25">
-        <v>8</v>
-      </c>
-      <c r="C22" s="48" t="s">
-        <v>42</v>
-      </c>
-      <c r="D22" s="49"/>
-      <c r="E22" s="49"/>
-      <c r="F22" s="50"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A23" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="B23" s="21">
-        <v>6</v>
-      </c>
-      <c r="C23" s="42"/>
-      <c r="D23" s="43"/>
-      <c r="E23" s="43"/>
-      <c r="F23" s="44"/>
-    </row>
-    <row r="24" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="28"/>
-      <c r="B24" s="23">
-        <v>7</v>
-      </c>
-      <c r="C24" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="D24" s="46"/>
-      <c r="E24" s="46"/>
-      <c r="F24" s="47"/>
-    </row>
-    <row r="25" spans="1:6" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="29"/>
-      <c r="B25" s="25">
-        <v>8</v>
-      </c>
-      <c r="C25" s="45" t="s">
-        <v>44</v>
-      </c>
-      <c r="D25" s="46"/>
-      <c r="E25" s="46"/>
-      <c r="F25" s="47"/>
-    </row>
-    <row r="26" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="30" t="s">
-        <v>26</v>
-      </c>
-      <c r="B26" s="31">
-        <v>1</v>
-      </c>
-      <c r="C26" s="58" t="s">
-        <v>34</v>
-      </c>
-      <c r="D26" s="59"/>
-      <c r="E26" s="59"/>
-      <c r="F26" s="60"/>
-    </row>
-    <row r="27" spans="1:6" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="32"/>
-      <c r="B27" s="25">
-        <v>2</v>
-      </c>
-      <c r="C27" s="61"/>
-      <c r="D27" s="62"/>
-      <c r="E27" s="62"/>
-      <c r="F27" s="63"/>
-    </row>
-    <row r="28" spans="1:6" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="33"/>
-      <c r="B28" s="34"/>
-      <c r="C28" s="64"/>
-      <c r="D28" s="65"/>
-      <c r="E28" s="65"/>
-      <c r="F28" s="66"/>
-    </row>
-    <row r="29" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="35"/>
-      <c r="B29" s="31" t="s">
+      <c r="D29" s="52"/>
+      <c r="E29" s="52"/>
+      <c r="F29" s="53"/>
+      <c r="G29" s="49" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="40"/>
+      <c r="B30" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="C30" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="55" t="s">
-        <v>32</v>
-      </c>
-      <c r="D29" s="56"/>
-      <c r="E29" s="56"/>
-      <c r="F29" s="57"/>
-    </row>
-    <row r="30" spans="1:6" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="36"/>
-      <c r="B30" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" s="48" t="s">
-        <v>30</v>
-      </c>
-      <c r="D30" s="49"/>
-      <c r="E30" s="49"/>
-      <c r="F30" s="50"/>
-    </row>
-    <row r="31" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="D30" s="55"/>
+      <c r="E30" s="55"/>
+      <c r="F30" s="56"/>
+      <c r="G30" s="48" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A32" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.4">
@@ -1548,6 +1711,11 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C21:F21"/>
     <mergeCell ref="C9:E9"/>
     <mergeCell ref="C29:F29"/>
     <mergeCell ref="C30:F30"/>
@@ -1564,11 +1732,6 @@
     <mergeCell ref="C14:F14"/>
     <mergeCell ref="C15:F15"/>
     <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C21:F21"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C6"/>
